--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -808,667 +808,682 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9873,0.0008,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.2286,0.0007,0.0118,0.8644</t>
-  </si>
-  <si>
-    <t>0.9484,0.0023,0.0148,0.0245</t>
-  </si>
-  <si>
-    <t>0.8198,0.0010,0.0368,0.0920</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9897,0.0007,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.3022,0.0006,0.0090,0.8267</t>
+  </si>
+  <si>
+    <t>0.9503,0.0017,0.0167,0.0165</t>
+  </si>
+  <si>
+    <t>0.8769,0.0013,0.0201,0.0835</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8891,0.0009,0.1431,0.0004</t>
+  </si>
+  <si>
+    <t>0.3850,0.0008,0.7889,0.0001</t>
+  </si>
+  <si>
+    <t>0.7675,0.0005,0.4269,0.0001</t>
+  </si>
+  <si>
+    <t>0.0124,0.0003,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.9729,0.0004,0.0438,0.0001</t>
+  </si>
+  <si>
+    <t>0.1424,0.8003,0.0249,0.0001</t>
+  </si>
+  <si>
+    <t>0.6358,0.2346,0.0656,0.0005</t>
+  </si>
+  <si>
+    <t>0.9121,0.0917,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.0553,0.9106,0.0406,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.9897,0.0125,0.0001</t>
+  </si>
+  <si>
+    <t>0.9571,0.0002,0.0577,0.0003</t>
+  </si>
+  <si>
+    <t>0.8601,0.0002,0.2385,0.0002</t>
+  </si>
+  <si>
+    <t>0.0546,0.0001,0.9748,0.0002</t>
+  </si>
+  <si>
+    <t>0.2972,0.0002,0.8291,0.0003</t>
+  </si>
+  <si>
+    <t>0.1829,0.0001,0.9132,0.0001</t>
+  </si>
+  <si>
+    <t>0.2901,0.0001,0.8415,0.0003</t>
+  </si>
+  <si>
+    <t>0.1974,0.0000,0.8973,0.0002</t>
+  </si>
+  <si>
+    <t>0.9887,0.0026,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9798,0.0014,0.0128,0.0008</t>
+  </si>
+  <si>
+    <t>0.0043,0.0002,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.3853,0.0143,0.5310,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0010,0.0103,0.0008</t>
+  </si>
+  <si>
+    <t>0.9911,0.0037,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9049,0.0360,0.0291,0.0011</t>
+  </si>
+  <si>
+    <t>0.0088,0.0252,0.9708,0.0001</t>
+  </si>
+  <si>
+    <t>0.0272,0.0003,0.9808,0.0003</t>
+  </si>
+  <si>
+    <t>0.0349,0.0004,0.9829,0.0001</t>
+  </si>
+  <si>
+    <t>0.2742,0.0001,0.8190,0.0006</t>
+  </si>
+  <si>
+    <t>0.0295,0.0000,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.0487,0.2327,0.5286,0.0000</t>
+  </si>
+  <si>
+    <t>0.0185,0.0006,0.9904,0.0002</t>
+  </si>
+  <si>
+    <t>0.9178,0.0042,0.0471,0.0148</t>
+  </si>
+  <si>
+    <t>0.0203,0.9528,0.0378,0.0013</t>
+  </si>
+  <si>
+    <t>0.0064,0.9843,0.0109,0.0002</t>
+  </si>
+  <si>
+    <t>0.0339,0.9153,0.1008,0.0016</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0081,0.0005,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0910,0.0001,0.9482,0.0004</t>
+  </si>
+  <si>
+    <t>0.0802,0.0000,0.9770,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.1270,0.0002,0.9468,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.0003,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0625,0.9854,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0005,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.2771,0.9888,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1278,0.7778,0.0700,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9930,0.0003,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.9835,0.0031,0.0089,0.0003</t>
+  </si>
+  <si>
+    <t>0.0124,0.0001,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0026,0.9949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0363,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.2979,0.9229,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.2927,0.9786,0.0000</t>
+  </si>
+  <si>
+    <t>0.1095,0.0008,0.1071,0.8159</t>
+  </si>
+  <si>
+    <t>0.0845,0.0008,0.0090,0.9565</t>
+  </si>
+  <si>
+    <t>0.2226,0.0003,0.0085,0.8598</t>
+  </si>
+  <si>
+    <t>0.1587,0.0007,0.0176,0.8919</t>
+  </si>
+  <si>
+    <t>0.3455,0.0006,0.0215,0.7245</t>
+  </si>
+  <si>
+    <t>0.1024,0.0009,0.0251,0.9171</t>
+  </si>
+  <si>
+    <t>0.0003,0.3937,0.9928,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0841,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0787,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0058,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3303,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0115,0.1074,0.9395,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
+    <t>0.0004,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.5358,0.0001,0.7561,0.0000</t>
+  </si>
+  <si>
+    <t>0.9436,0.0007,0.0469,0.0018</t>
+  </si>
+  <si>
+    <t>0.4628,0.0001,0.7953,0.0000</t>
+  </si>
+  <si>
+    <t>0.5624,0.4410,0.0123,0.0002</t>
+  </si>
+  <si>
+    <t>0.6168,0.3502,0.0202,0.0004</t>
+  </si>
+  <si>
+    <t>0.9402,0.0468,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9548,0.0294,0.0086,0.0015</t>
+  </si>
+  <si>
+    <t>0.5632,0.3898,0.0272,0.0006</t>
+  </si>
+  <si>
+    <t>0.0233,0.9653,0.0171,0.0001</t>
+  </si>
+  <si>
+    <t>0.9864,0.0110,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9477,0.0010,0.0411,0.0028</t>
+  </si>
+  <si>
+    <t>0.8458,0.0003,0.2753,0.0003</t>
+  </si>
+  <si>
+    <t>0.8067,0.0041,0.2162,0.0015</t>
+  </si>
+  <si>
+    <t>0.8076,0.0004,0.3237,0.0002</t>
+  </si>
+  <si>
+    <t>0.7333,0.0090,0.1302,0.1313</t>
+  </si>
+  <si>
+    <t>0.0145,0.9702,0.0177,0.0003</t>
+  </si>
+  <si>
+    <t>0.0068,0.9853,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.2578,0.5381,0.1668,0.0082</t>
+  </si>
+  <si>
+    <t>0.0003,0.7153,0.9856,0.0000</t>
+  </si>
+  <si>
+    <t>0.8676,0.0667,0.0262,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0029,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.9920,0.0025,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0054,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0800,0.0001,0.9631,0.0001</t>
+  </si>
+  <si>
+    <t>0.9842,0.0005,0.0111,0.0006</t>
+  </si>
+  <si>
+    <t>0.9233,0.0022,0.0771,0.0010</t>
+  </si>
+  <si>
+    <t>0.7704,0.0001,0.3769,0.0003</t>
+  </si>
+  <si>
+    <t>0.9580,0.0006,0.0336,0.0007</t>
+  </si>
+  <si>
+    <t>0.8576,0.0010,0.0187,0.1058</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.0037,0.9978</t>
+  </si>
+  <si>
+    <t>0.0383,0.0003,0.0085,0.9751</t>
+  </si>
+  <si>
+    <t>0.1161,0.0006,0.0097,0.9377</t>
+  </si>
+  <si>
+    <t>0.0071,0.2619,0.9309,0.0001</t>
+  </si>
+  <si>
+    <t>0.9658,0.0126,0.0097,0.0035</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9772,0.0094,0.0060,0.0011</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9794,0.0005,0.0100,0.0022</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0526,0.0003,0.9669,0.0026</t>
+  </si>
+  <si>
+    <t>0.9937,0.0003,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0004,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9796,0.0066,0.0079,0.0007</t>
+  </si>
+  <si>
+    <t>0.9841,0.0021,0.0052,0.0028</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8582,0.0373,0.0716,0.0018</t>
+  </si>
+  <si>
+    <t>0.9934,0.0008,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9950,0.0004,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9992,0.0002,0.0001,0.0001</t>
   </si>
   <si>
+    <t>0.9983,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9846,0.0048,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.9826,0.0057,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.9832,0.0020,0.0082,0.0020</t>
+  </si>
+  <si>
+    <t>0.9906,0.0025,0.0019,0.0040</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0016,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0016,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.0113,0.0000,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0153,0.0009,0.9825,0.0014</t>
+  </si>
+  <si>
+    <t>0.0824,0.0001,0.9711,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0050,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0312,0.0000,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0079,0.0000,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0086,0.0001,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.4594,0.0012,0.6893,0.0008</t>
+  </si>
+  <si>
+    <t>0.5386,0.0012,0.5744,0.0014</t>
+  </si>
+  <si>
+    <t>0.6597,0.0035,0.4676,0.0005</t>
+  </si>
+  <si>
+    <t>0.4598,0.0010,0.7472,0.0001</t>
+  </si>
+  <si>
+    <t>0.8440,0.0004,0.3391,0.0000</t>
+  </si>
+  <si>
+    <t>0.9192,0.0004,0.1471,0.0001</t>
+  </si>
+  <si>
+    <t>0.8521,0.0004,0.2648,0.0002</t>
+  </si>
+  <si>
+    <t>0.9380,0.0003,0.1032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9769,0.0182,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0020,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9418,0.0014,0.0432,0.0016</t>
+  </si>
+  <si>
+    <t>0.9801,0.0002,0.0205,0.0003</t>
+  </si>
+  <si>
+    <t>0.9439,0.0006,0.0380,0.0035</t>
+  </si>
+  <si>
+    <t>0.9160,0.0002,0.1444,0.0003</t>
+  </si>
+  <si>
+    <t>0.9190,0.0007,0.1200,0.0006</t>
+  </si>
+  <si>
+    <t>0.0054,0.0001,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0188,0.0004,0.9864,0.0005</t>
+  </si>
+  <si>
+    <t>0.0402,0.0001,0.9824,0.0001</t>
+  </si>
+  <si>
+    <t>0.0199,0.0011,0.9872,0.0001</t>
+  </si>
+  <si>
+    <t>0.0277,0.0001,0.9854,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
     <t>0.9996,0.0002,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.8820,0.0004,0.1848,0.0002</t>
-  </si>
-  <si>
-    <t>0.8458,0.0003,0.3385,0.0001</t>
-  </si>
-  <si>
-    <t>0.6888,0.0005,0.5487,0.0001</t>
-  </si>
-  <si>
-    <t>0.0282,0.0002,0.9888,0.0001</t>
-  </si>
-  <si>
-    <t>0.9488,0.0004,0.0802,0.0003</t>
-  </si>
-  <si>
-    <t>0.2340,0.6344,0.0682,0.0003</t>
-  </si>
-  <si>
-    <t>0.3242,0.5706,0.0556,0.0003</t>
-  </si>
-  <si>
-    <t>0.9548,0.0374,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.0202,0.9709,0.0092,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.9902,0.0097,0.0001</t>
-  </si>
-  <si>
-    <t>0.6679,0.0007,0.4287,0.0013</t>
-  </si>
-  <si>
-    <t>0.6858,0.0004,0.3971,0.0011</t>
-  </si>
-  <si>
-    <t>0.0734,0.0001,0.9655,0.0001</t>
-  </si>
-  <si>
-    <t>0.0850,0.0001,0.9547,0.0005</t>
-  </si>
-  <si>
-    <t>0.0908,0.0001,0.9632,0.0001</t>
-  </si>
-  <si>
-    <t>0.3301,0.0001,0.8044,0.0004</t>
-  </si>
-  <si>
-    <t>0.1066,0.0001,0.9453,0.0003</t>
-  </si>
-  <si>
-    <t>0.9695,0.0064,0.0130,0.0003</t>
-  </si>
-  <si>
-    <t>0.9819,0.0015,0.0117,0.0006</t>
-  </si>
-  <si>
-    <t>0.0044,0.0004,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.1604,0.0066,0.8456,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9901,0.0010,0.0038,0.0026</t>
-  </si>
-  <si>
-    <t>0.9855,0.0058,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.8364,0.0804,0.0437,0.0008</t>
-  </si>
-  <si>
-    <t>0.0294,0.0130,0.9484,0.0002</t>
-  </si>
-  <si>
-    <t>0.0285,0.0003,0.9832,0.0001</t>
-  </si>
-  <si>
-    <t>0.0436,0.0006,0.9723,0.0002</t>
-  </si>
-  <si>
-    <t>0.1159,0.0002,0.9116,0.0022</t>
-  </si>
-  <si>
-    <t>0.0288,0.0005,0.9820,0.0000</t>
-  </si>
-  <si>
-    <t>0.0957,0.5957,0.1331,0.0003</t>
-  </si>
-  <si>
-    <t>0.0321,0.0004,0.9837,0.0002</t>
-  </si>
-  <si>
-    <t>0.7873,0.0094,0.1196,0.0539</t>
-  </si>
-  <si>
-    <t>0.0149,0.9642,0.0290,0.0021</t>
-  </si>
-  <si>
-    <t>0.1077,0.8122,0.0485,0.0013</t>
-  </si>
-  <si>
-    <t>0.0204,0.9552,0.0334,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0087,0.0003,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0762,0.0001,0.9731,0.0000</t>
-  </si>
-  <si>
-    <t>0.1221,0.0000,0.9546,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0408,0.0002,0.9802,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0087,0.0013,0.9941,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.3124,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.0001,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.3657,0.9901,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0502,0.8963,0.0582,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9976,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9919,0.0002,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.9911,0.0014,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.0002,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0158,0.0722,0.8989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0056,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0081,0.3923,0.8233,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0445,0.9921,0.0000</t>
-  </si>
-  <si>
-    <t>0.0556,0.0012,0.2042,0.8382</t>
-  </si>
-  <si>
-    <t>0.1007,0.0008,0.0107,0.9436</t>
-  </si>
-  <si>
-    <t>0.6861,0.0005,0.0268,0.2413</t>
-  </si>
-  <si>
-    <t>0.0740,0.0006,0.0095,0.9590</t>
-  </si>
-  <si>
-    <t>0.4440,0.0010,0.0190,0.6506</t>
-  </si>
-  <si>
-    <t>0.0434,0.0006,0.0061,0.9785</t>
-  </si>
-  <si>
-    <t>0.0002,0.5917,0.9883,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0177,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0614,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0013,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.2361,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0389,0.0015,0.9730,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0011,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.3293,0.0005,0.8386,0.0001</t>
-  </si>
-  <si>
-    <t>0.9059,0.0010,0.0884,0.0021</t>
-  </si>
-  <si>
-    <t>0.0488,0.0001,0.9769,0.0002</t>
-  </si>
-  <si>
-    <t>0.5176,0.4881,0.0143,0.0002</t>
-  </si>
-  <si>
-    <t>0.3578,0.5289,0.0639,0.0007</t>
-  </si>
-  <si>
-    <t>0.8816,0.1057,0.0089,0.0009</t>
-  </si>
-  <si>
-    <t>0.9728,0.0148,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.8328,0.1383,0.0162,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.9812,0.0064,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0044,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9078,0.0028,0.0975,0.0010</t>
-  </si>
-  <si>
-    <t>0.6767,0.0002,0.5425,0.0002</t>
-  </si>
-  <si>
-    <t>0.8842,0.0044,0.1141,0.0025</t>
-  </si>
-  <si>
-    <t>0.8841,0.0011,0.1767,0.0003</t>
-  </si>
-  <si>
-    <t>0.7208,0.0145,0.1499,0.1117</t>
-  </si>
-  <si>
-    <t>0.0169,0.9633,0.0203,0.0003</t>
-  </si>
-  <si>
-    <t>0.0123,0.9739,0.0140,0.0003</t>
-  </si>
-  <si>
-    <t>0.1167,0.7674,0.1405,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.8184,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.7912,0.0927,0.0611,0.0007</t>
-  </si>
-  <si>
-    <t>0.9911,0.0041,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.9925,0.0023,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.0024,0.0020,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.0011,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0002,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.1007,0.0001,0.9586,0.0000</t>
-  </si>
-  <si>
-    <t>0.9731,0.0005,0.0185,0.0014</t>
-  </si>
-  <si>
-    <t>0.9593,0.0005,0.0590,0.0002</t>
-  </si>
-  <si>
-    <t>0.4834,0.0001,0.7108,0.0002</t>
-  </si>
-  <si>
-    <t>0.9745,0.0005,0.0243,0.0004</t>
-  </si>
-  <si>
-    <t>0.8230,0.0010,0.0228,0.1402</t>
-  </si>
-  <si>
-    <t>0.0027,0.0003,0.0020,0.9982</t>
-  </si>
-  <si>
-    <t>0.0607,0.0003,0.0126,0.9564</t>
-  </si>
-  <si>
-    <t>0.0886,0.0012,0.0094,0.9555</t>
-  </si>
-  <si>
-    <t>0.0026,0.3764,0.9626,0.0001</t>
-  </si>
-  <si>
-    <t>0.6507,0.2839,0.0423,0.0042</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0142,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9880,0.0002,0.0070,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0295,0.0014,0.9749,0.0034</t>
-  </si>
-  <si>
-    <t>0.9930,0.0003,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9766,0.0050,0.0121,0.0011</t>
-  </si>
-  <si>
-    <t>0.9936,0.0007,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0006,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.8695,0.0469,0.0477,0.0015</t>
-  </si>
-  <si>
-    <t>0.9928,0.0006,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0005,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9797,0.0068,0.0042,0.0027</t>
-  </si>
-  <si>
-    <t>0.9617,0.0097,0.0128,0.0014</t>
-  </si>
-  <si>
-    <t>0.4364,0.0012,0.6993,0.0010</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9871,0.0020,0.0019,0.0090</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0122,0.0000,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0642,0.0002,0.9625,0.0002</t>
-  </si>
-  <si>
-    <t>0.1457,0.0001,0.9469,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0025,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.1622,0.0001,0.9310,0.0001</t>
-  </si>
-  <si>
-    <t>0.0759,0.0001,0.9723,0.0001</t>
-  </si>
-  <si>
-    <t>0.0181,0.0001,0.9929,0.0002</t>
-  </si>
-  <si>
-    <t>0.4011,0.0011,0.7250,0.0013</t>
-  </si>
-  <si>
-    <t>0.8372,0.0004,0.2541,0.0005</t>
-  </si>
-  <si>
-    <t>0.8846,0.0025,0.1479,0.0005</t>
-  </si>
-  <si>
-    <t>0.3363,0.0012,0.8261,0.0002</t>
-  </si>
-  <si>
-    <t>0.5122,0.0012,0.6882,0.0001</t>
-  </si>
-  <si>
-    <t>0.9906,0.0002,0.0131,0.0000</t>
-  </si>
-  <si>
-    <t>0.9186,0.0007,0.1272,0.0004</t>
-  </si>
-  <si>
-    <t>0.9432,0.0009,0.0665,0.0010</t>
-  </si>
-  <si>
-    <t>0.9893,0.0052,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0042,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0024,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0056,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9081,0.0022,0.1001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9810,0.0003,0.0218,0.0002</t>
-  </si>
-  <si>
-    <t>0.9452,0.0014,0.0295,0.0054</t>
-  </si>
-  <si>
-    <t>0.9036,0.0003,0.1600,0.0003</t>
-  </si>
-  <si>
-    <t>0.9398,0.0006,0.0939,0.0003</t>
-  </si>
-  <si>
-    <t>0.0166,0.0002,0.9910,0.0004</t>
-  </si>
-  <si>
-    <t>0.0225,0.0003,0.9815,0.0016</t>
-  </si>
-  <si>
-    <t>0.0852,0.0001,0.9586,0.0002</t>
-  </si>
-  <si>
-    <t>0.0379,0.0003,0.9785,0.0001</t>
-  </si>
-  <si>
-    <t>0.0330,0.0003,0.9789,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6507,0.0002,0.5560,0.0002</t>
-  </si>
-  <si>
-    <t>0.9437,0.0006,0.0842,0.0004</t>
-  </si>
-  <si>
-    <t>0.9915,0.0005,0.0025,0.0018</t>
-  </si>
-  <si>
-    <t>0.0393,0.0000,0.9889,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0003,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0452,0.0027,0.9704,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0604,0.0002,0.9723,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0137,0.0000,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0514,0.0017,0.9697,0.0007</t>
-  </si>
-  <si>
-    <t>0.8079,0.0002,0.3096,0.0004</t>
-  </si>
-  <si>
-    <t>0.8859,0.0009,0.1296,0.0013</t>
-  </si>
-  <si>
-    <t>0.9329,0.0005,0.0469,0.0039</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0128,0.0002,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0189,0.0002,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0240,0.0012,0.9863,0.0002</t>
-  </si>
-  <si>
-    <t>0.0170,0.0000,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.1532,0.0006,0.8614,0.0054</t>
-  </si>
-  <si>
-    <t>0.2413,0.0002,0.8606,0.0003</t>
-  </si>
-  <si>
-    <t>0.0765,0.0001,0.9525,0.0003</t>
-  </si>
-  <si>
-    <t>0.9756,0.0003,0.0036,0.0117</t>
-  </si>
-  <si>
-    <t>0.1208,0.0013,0.0208,0.9005</t>
-  </si>
-  <si>
-    <t>0.7505,0.0003,0.0205,0.1690</t>
-  </si>
-  <si>
-    <t>0.0155,0.0005,0.0067,0.9905</t>
-  </si>
-  <si>
-    <t>0.0158,0.0004,0.0029,0.9924</t>
-  </si>
-  <si>
-    <t>0.9664,0.0009,0.0139,0.0067</t>
+    <t>0.9995,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.4917,0.0003,0.7177,0.0002</t>
+  </si>
+  <si>
+    <t>0.9413,0.0028,0.0654,0.0004</t>
+  </si>
+  <si>
+    <t>0.9901,0.0004,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.0242,0.0000,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0169,0.0021,0.9893,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0423,0.0003,0.9778,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0000,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0111,0.0000,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0300,0.0008,0.9821,0.0013</t>
+  </si>
+  <si>
+    <t>0.5945,0.0002,0.4977,0.0018</t>
+  </si>
+  <si>
+    <t>0.8869,0.0003,0.1637,0.0005</t>
+  </si>
+  <si>
+    <t>0.9659,0.0004,0.0276,0.0010</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0196,0.0003,0.9884,0.0000</t>
+  </si>
+  <si>
+    <t>0.0074,0.0001,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0138,0.0002,0.9943,0.0000</t>
+  </si>
+  <si>
+    <t>0.0602,0.0011,0.9660,0.0001</t>
+  </si>
+  <si>
+    <t>0.0194,0.0001,0.9877,0.0003</t>
+  </si>
+  <si>
+    <t>0.0798,0.0015,0.9225,0.0197</t>
+  </si>
+  <si>
+    <t>0.4586,0.0002,0.6506,0.0004</t>
+  </si>
+  <si>
+    <t>0.0253,0.0001,0.9845,0.0002</t>
+  </si>
+  <si>
+    <t>0.9727,0.0005,0.0071,0.0093</t>
+  </si>
+  <si>
+    <t>0.1555,0.0009,0.0095,0.8856</t>
+  </si>
+  <si>
+    <t>0.2338,0.0004,0.0299,0.7576</t>
+  </si>
+  <si>
+    <t>0.0175,0.0005,0.0058,0.9899</t>
+  </si>
+  <si>
+    <t>0.0148,0.0003,0.0024,0.9933</t>
+  </si>
+  <si>
+    <t>0.9384,0.0009,0.0232,0.0155</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1868,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1882,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1896,7 +1911,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1910,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1924,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1938,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1952,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1966,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2008,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2022,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2033,10 +2048,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2047,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2064,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2078,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2092,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2103,10 +2118,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2120,7 +2135,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2134,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2148,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2162,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,7 +2191,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2233,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,7 +2247,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2289,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,7 +2345,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2414,7 +2429,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2443,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2439,10 +2454,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,7 +2485,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2513,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2929,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>340</v>
@@ -2985,7 +3000,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D83" t="s">
         <v>344</v>
@@ -3072,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3086,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3100,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3114,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3184,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3212,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3226,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3240,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3282,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>321</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3296,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3307,10 +3322,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3352,7 +3367,7 @@
         <v>259</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3363,10 +3378,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3380,7 +3395,7 @@
         <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3394,7 +3409,7 @@
         <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3408,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3436,7 +3451,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3450,7 +3465,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3461,10 +3476,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3478,7 +3493,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,7 +3507,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3506,7 +3521,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3520,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3534,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3591,7 @@
         <v>259</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,7 +3605,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3618,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3632,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3646,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3660,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3674,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3730,7 +3745,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3744,7 +3759,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3758,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3772,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3786,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3800,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3811,10 +3826,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3828,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3842,7 +3857,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3856,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3870,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3926,7 +3941,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3940,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3954,7 +3969,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3968,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3982,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,7 +4109,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4108,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4178,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4192,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>352</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4234,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4248,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4262,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4276,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4287,10 +4302,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4304,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>419</v>
+        <v>350</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4318,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4332,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>268</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4346,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4360,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4374,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4388,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4402,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4416,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4430,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4444,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4458,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4472,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4486,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4497,10 +4512,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,7 +4529,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4539,10 +4554,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4556,7 +4571,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4570,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4598,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4612,7 +4627,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4640,7 +4655,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4668,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4682,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4696,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4724,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4738,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4752,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4766,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4794,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4808,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>272</v>
+        <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4836,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>268</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4850,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>419</v>
+        <v>355</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4864,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>419</v>
+        <v>275</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4878,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>270</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4892,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>271</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4934,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,7 +5005,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>322</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>322</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5144,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>409</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5158,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>469</v>
+        <v>415</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5172,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>470</v>
+        <v>319</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5186,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5200,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5214,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>419</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5228,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5242,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5256,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5270,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5284,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5312,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5326,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5354,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5365,10 +5380,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5382,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5396,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5410,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
